--- a/访谈准备资料/人生五年访谈思路清单，二版.xlsx
+++ b/访谈准备资料/人生五年访谈思路清单，二版.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\以前d盘\笔记汇总\git\百家职业共享大全\共创专区\模板\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\以前d盘\笔记汇总\git\人生五年\访谈准备资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD5AD1A9-1B4D-4A69-B105-86B290A4FE76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE92C1EE-874F-493B-97D8-708EBA855967}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
